--- a/data/nzd0175/nzd0175.xlsx
+++ b/data/nzd0175/nzd0175.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U356"/>
+  <dimension ref="A1:U360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25016,6 +25016,282 @@
         <v>366.5</v>
       </c>
       <c r="U356" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>312.92</v>
+      </c>
+      <c r="C357" t="n">
+        <v>299.08</v>
+      </c>
+      <c r="D357" t="n">
+        <v>298.13</v>
+      </c>
+      <c r="E357" t="n">
+        <v>314.33</v>
+      </c>
+      <c r="F357" t="n">
+        <v>300.29</v>
+      </c>
+      <c r="G357" t="n">
+        <v>292.38</v>
+      </c>
+      <c r="H357" t="n">
+        <v>299.03</v>
+      </c>
+      <c r="I357" t="n">
+        <v>308.67</v>
+      </c>
+      <c r="J357" t="n">
+        <v>317.44</v>
+      </c>
+      <c r="K357" t="n">
+        <v>321.1</v>
+      </c>
+      <c r="L357" t="n">
+        <v>329.7</v>
+      </c>
+      <c r="M357" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="N357" t="n">
+        <v>356.26</v>
+      </c>
+      <c r="O357" t="n">
+        <v>361.19</v>
+      </c>
+      <c r="P357" t="n">
+        <v>371.17</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>368.03</v>
+      </c>
+      <c r="R357" t="n">
+        <v>376.99</v>
+      </c>
+      <c r="S357" t="n">
+        <v>372.94</v>
+      </c>
+      <c r="T357" t="n">
+        <v>365.48</v>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>312.31</v>
+      </c>
+      <c r="C358" t="n">
+        <v>298.22</v>
+      </c>
+      <c r="D358" t="n">
+        <v>298.21</v>
+      </c>
+      <c r="E358" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="F358" t="n">
+        <v>301.76</v>
+      </c>
+      <c r="G358" t="n">
+        <v>293.41</v>
+      </c>
+      <c r="H358" t="n">
+        <v>299.37</v>
+      </c>
+      <c r="I358" t="n">
+        <v>310.21</v>
+      </c>
+      <c r="J358" t="n">
+        <v>319.1</v>
+      </c>
+      <c r="K358" t="n">
+        <v>323.09</v>
+      </c>
+      <c r="L358" t="n">
+        <v>331.62</v>
+      </c>
+      <c r="M358" t="n">
+        <v>343.41</v>
+      </c>
+      <c r="N358" t="n">
+        <v>356.45</v>
+      </c>
+      <c r="O358" t="n">
+        <v>361.11</v>
+      </c>
+      <c r="P358" t="n">
+        <v>371.39</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>368.16</v>
+      </c>
+      <c r="R358" t="n">
+        <v>378.8</v>
+      </c>
+      <c r="S358" t="n">
+        <v>372.87</v>
+      </c>
+      <c r="T358" t="n">
+        <v>367.31</v>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>311.74</v>
+      </c>
+      <c r="C359" t="n">
+        <v>298.43</v>
+      </c>
+      <c r="D359" t="n">
+        <v>298.7</v>
+      </c>
+      <c r="E359" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="F359" t="n">
+        <v>301.59</v>
+      </c>
+      <c r="G359" t="n">
+        <v>293.74</v>
+      </c>
+      <c r="H359" t="n">
+        <v>300.06</v>
+      </c>
+      <c r="I359" t="n">
+        <v>311.12</v>
+      </c>
+      <c r="J359" t="n">
+        <v>320.12</v>
+      </c>
+      <c r="K359" t="n">
+        <v>323.86</v>
+      </c>
+      <c r="L359" t="n">
+        <v>332.91</v>
+      </c>
+      <c r="M359" t="n">
+        <v>345.99</v>
+      </c>
+      <c r="N359" t="n">
+        <v>357.77</v>
+      </c>
+      <c r="O359" t="n">
+        <v>361.29</v>
+      </c>
+      <c r="P359" t="n">
+        <v>371.37</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>368.49</v>
+      </c>
+      <c r="R359" t="n">
+        <v>378.63</v>
+      </c>
+      <c r="S359" t="n">
+        <v>372.54</v>
+      </c>
+      <c r="T359" t="n">
+        <v>366.74</v>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>310.81</v>
+      </c>
+      <c r="C360" t="n">
+        <v>297.56</v>
+      </c>
+      <c r="D360" t="n">
+        <v>298.85</v>
+      </c>
+      <c r="E360" t="n">
+        <v>316.54</v>
+      </c>
+      <c r="F360" t="n">
+        <v>302.16</v>
+      </c>
+      <c r="G360" t="n">
+        <v>294.93</v>
+      </c>
+      <c r="H360" t="n">
+        <v>301.27</v>
+      </c>
+      <c r="I360" t="n">
+        <v>310.38</v>
+      </c>
+      <c r="J360" t="n">
+        <v>318.13</v>
+      </c>
+      <c r="K360" t="n">
+        <v>324.59</v>
+      </c>
+      <c r="L360" t="n">
+        <v>332.98</v>
+      </c>
+      <c r="M360" t="n">
+        <v>346.21</v>
+      </c>
+      <c r="N360" t="n">
+        <v>359.59</v>
+      </c>
+      <c r="O360" t="n">
+        <v>361.89</v>
+      </c>
+      <c r="P360" t="n">
+        <v>371.54</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>369.74</v>
+      </c>
+      <c r="R360" t="n">
+        <v>380.89</v>
+      </c>
+      <c r="S360" t="n">
+        <v>373.37</v>
+      </c>
+      <c r="T360" t="n">
+        <v>367.09</v>
+      </c>
+      <c r="U360" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25032,7 +25308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:B370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28695,6 +28971,46 @@
       </c>
       <c r="B366" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>-0.32</v>
       </c>
     </row>
   </sheetData>
@@ -28863,28 +29179,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3486143472292855</v>
+        <v>0.3449456417005079</v>
       </c>
       <c r="J2" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K2" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1730195951825623</v>
+        <v>0.1733708416403398</v>
       </c>
       <c r="M2" t="n">
-        <v>4.308538351364213</v>
+        <v>4.279963070032792</v>
       </c>
       <c r="N2" t="n">
-        <v>31.80530847775505</v>
+        <v>31.48749305439564</v>
       </c>
       <c r="O2" t="n">
-        <v>5.639619533067373</v>
+        <v>5.611371762269511</v>
       </c>
       <c r="P2" t="n">
-        <v>304.1985610841822</v>
+        <v>304.2387940276628</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28941,28 +29257,28 @@
         <v>0.1504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06601484531676112</v>
+        <v>-0.06750497853618832</v>
       </c>
       <c r="J3" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K3" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007248511842765426</v>
+        <v>0.007763568371725982</v>
       </c>
       <c r="M3" t="n">
-        <v>4.189240234638918</v>
+        <v>4.151055420532471</v>
       </c>
       <c r="N3" t="n">
-        <v>32.68015332412971</v>
+        <v>32.32417812636177</v>
       </c>
       <c r="O3" t="n">
-        <v>5.71665578149758</v>
+        <v>5.685435614476852</v>
       </c>
       <c r="P3" t="n">
-        <v>300.7790242743171</v>
+        <v>300.7953700335567</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29019,28 +29335,28 @@
         <v>0.1503</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06627033351980929</v>
+        <v>-0.0728006612080358</v>
       </c>
       <c r="J4" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K4" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008470530206213023</v>
+        <v>0.01042219445938619</v>
       </c>
       <c r="M4" t="n">
-        <v>3.941735655011681</v>
+        <v>3.930805757548623</v>
       </c>
       <c r="N4" t="n">
-        <v>28.14767417392079</v>
+        <v>27.92952304861855</v>
       </c>
       <c r="O4" t="n">
-        <v>5.305438169832987</v>
+        <v>5.284838980387061</v>
       </c>
       <c r="P4" t="n">
-        <v>303.226018480239</v>
+        <v>303.2975916470742</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29097,28 +29413,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04818964902624645</v>
+        <v>-0.04995185710282357</v>
       </c>
       <c r="J5" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01001889845213166</v>
+        <v>0.01101131205435291</v>
       </c>
       <c r="M5" t="n">
-        <v>2.663230322879148</v>
+        <v>2.641716041413675</v>
       </c>
       <c r="N5" t="n">
-        <v>12.56387559234889</v>
+        <v>12.43820267662625</v>
       </c>
       <c r="O5" t="n">
-        <v>3.544555767984034</v>
+        <v>3.526783616360131</v>
       </c>
       <c r="P5" t="n">
-        <v>317.7678311244414</v>
+        <v>317.7871286883428</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29175,28 +29491,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04781129328422732</v>
+        <v>0.04748523867438404</v>
       </c>
       <c r="J6" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K6" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007421719000070492</v>
+        <v>0.007501294039281459</v>
       </c>
       <c r="M6" t="n">
-        <v>3.166846247033047</v>
+        <v>3.136686240966863</v>
       </c>
       <c r="N6" t="n">
-        <v>16.73903491258167</v>
+        <v>16.55819938083391</v>
       </c>
       <c r="O6" t="n">
-        <v>4.091336567991158</v>
+        <v>4.069176744850721</v>
       </c>
       <c r="P6" t="n">
-        <v>300.3087780420874</v>
+        <v>300.3123369866958</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29253,28 +29569,28 @@
         <v>0.0881</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1132585944576712</v>
+        <v>0.111105376607242</v>
       </c>
       <c r="J7" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K7" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03054593619568613</v>
+        <v>0.0301195317470464</v>
       </c>
       <c r="M7" t="n">
-        <v>3.803071670743236</v>
+        <v>3.772982990727903</v>
       </c>
       <c r="N7" t="n">
-        <v>22.29078187468119</v>
+        <v>22.0618662219705</v>
       </c>
       <c r="O7" t="n">
-        <v>4.721311457072197</v>
+        <v>4.697006091327805</v>
       </c>
       <c r="P7" t="n">
-        <v>291.536288087836</v>
+        <v>291.5598679687994</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29331,28 +29647,28 @@
         <v>0.1029</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3462995951508263</v>
+        <v>0.3445229923471364</v>
       </c>
       <c r="J8" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K8" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1693333327401693</v>
+        <v>0.1713135929927209</v>
       </c>
       <c r="M8" t="n">
-        <v>4.585381851258705</v>
+        <v>4.545094734636794</v>
       </c>
       <c r="N8" t="n">
-        <v>32.21050002169016</v>
+        <v>31.86668667150159</v>
       </c>
       <c r="O8" t="n">
-        <v>5.675429501076563</v>
+        <v>5.645058606560394</v>
       </c>
       <c r="P8" t="n">
-        <v>291.3917143163197</v>
+        <v>291.4111676767557</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29409,28 +29725,28 @@
         <v>0.1076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.290758933298203</v>
+        <v>0.2956614247318045</v>
       </c>
       <c r="J9" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K9" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1196903686408657</v>
+        <v>0.1257592208281197</v>
       </c>
       <c r="M9" t="n">
-        <v>4.768037436949993</v>
+        <v>4.738527136325964</v>
       </c>
       <c r="N9" t="n">
-        <v>34.0448601200686</v>
+        <v>33.72738348971888</v>
       </c>
       <c r="O9" t="n">
-        <v>5.834797350385752</v>
+        <v>5.807528173820501</v>
       </c>
       <c r="P9" t="n">
-        <v>300.0242900768182</v>
+        <v>299.9705360184526</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29487,28 +29803,28 @@
         <v>0.1135</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1577592983810374</v>
+        <v>0.1669663216002085</v>
       </c>
       <c r="J10" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K10" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04418288657479641</v>
+        <v>0.05007744887664189</v>
       </c>
       <c r="M10" t="n">
-        <v>4.349429138195616</v>
+        <v>4.351919248611699</v>
       </c>
       <c r="N10" t="n">
-        <v>29.47948008550809</v>
+        <v>29.34984811017902</v>
       </c>
       <c r="O10" t="n">
-        <v>5.429500905747055</v>
+        <v>5.417550009937981</v>
       </c>
       <c r="P10" t="n">
-        <v>310.2602316156314</v>
+        <v>310.1593026166126</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29565,28 +29881,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2595985887890675</v>
+        <v>0.2600726040973741</v>
       </c>
       <c r="J11" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K11" t="n">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1216730643397586</v>
+        <v>0.1246569889382021</v>
       </c>
       <c r="M11" t="n">
-        <v>3.847434540122679</v>
+        <v>3.816856357939955</v>
       </c>
       <c r="N11" t="n">
-        <v>26.7476954110324</v>
+        <v>26.46734405512959</v>
       </c>
       <c r="O11" t="n">
-        <v>5.171817418570806</v>
+        <v>5.144642266973437</v>
       </c>
       <c r="P11" t="n">
-        <v>315.9433817104776</v>
+        <v>315.9381587295577</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29643,28 +29959,28 @@
         <v>0.1208</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1987669628712726</v>
+        <v>0.2041948657062745</v>
       </c>
       <c r="J12" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K12" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05976193947444153</v>
+        <v>0.0641867081937747</v>
       </c>
       <c r="M12" t="n">
-        <v>4.557086913290258</v>
+        <v>4.530808331272719</v>
       </c>
       <c r="N12" t="n">
-        <v>34.03382168239621</v>
+        <v>33.73928224099156</v>
       </c>
       <c r="O12" t="n">
-        <v>5.833851359299121</v>
+        <v>5.808552508240892</v>
       </c>
       <c r="P12" t="n">
-        <v>323.9751364565766</v>
+        <v>323.9156089926469</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29721,28 +30037,28 @@
         <v>0.1693</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2063792729683656</v>
+        <v>0.2176253176905744</v>
       </c>
       <c r="J13" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K13" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07337290521738637</v>
+        <v>0.08198180884673645</v>
       </c>
       <c r="M13" t="n">
-        <v>4.154833765466264</v>
+        <v>4.153527019315558</v>
       </c>
       <c r="N13" t="n">
-        <v>29.45171623097553</v>
+        <v>29.43436862566851</v>
       </c>
       <c r="O13" t="n">
-        <v>5.426943544111688</v>
+        <v>5.425345023652276</v>
       </c>
       <c r="P13" t="n">
-        <v>333.7995916262452</v>
+        <v>333.6762809880516</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29799,28 +30115,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1511852896682452</v>
+        <v>0.1587333918144416</v>
       </c>
       <c r="J14" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K14" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04599805746273622</v>
+        <v>0.05139256402653847</v>
       </c>
       <c r="M14" t="n">
-        <v>3.836663283786224</v>
+        <v>3.819354929820201</v>
       </c>
       <c r="N14" t="n">
-        <v>25.95601471928554</v>
+        <v>25.81219452258496</v>
       </c>
       <c r="O14" t="n">
-        <v>5.094704576252242</v>
+        <v>5.080570295014621</v>
       </c>
       <c r="P14" t="n">
-        <v>350.0151839336756</v>
+        <v>349.9324160305046</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29877,28 +30193,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.233511505229501</v>
+        <v>0.2371714799790894</v>
       </c>
       <c r="J15" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K15" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09556814218176868</v>
+        <v>0.1004092991853535</v>
       </c>
       <c r="M15" t="n">
-        <v>3.986007952493838</v>
+        <v>3.95562859844839</v>
       </c>
       <c r="N15" t="n">
-        <v>28.2545533422567</v>
+        <v>27.97035937208535</v>
       </c>
       <c r="O15" t="n">
-        <v>5.315501231516808</v>
+        <v>5.288701104438154</v>
       </c>
       <c r="P15" t="n">
-        <v>353.407181637038</v>
+        <v>353.3670576096966</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29955,28 +30271,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3245525356763171</v>
+        <v>0.3281380989658074</v>
       </c>
       <c r="J16" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K16" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1866187989427969</v>
+        <v>0.1936364276109075</v>
       </c>
       <c r="M16" t="n">
-        <v>3.886619352741398</v>
+        <v>3.853541005465373</v>
       </c>
       <c r="N16" t="n">
-        <v>25.11924328110433</v>
+        <v>24.86718840517504</v>
       </c>
       <c r="O16" t="n">
-        <v>5.0119101429599</v>
+        <v>4.986701154588576</v>
       </c>
       <c r="P16" t="n">
-        <v>360.9792229071793</v>
+        <v>360.9398586204454</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30033,28 +30349,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3739797405012499</v>
+        <v>0.3663240032958309</v>
       </c>
       <c r="J17" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K17" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2756643548620858</v>
+        <v>0.2710277729132992</v>
       </c>
       <c r="M17" t="n">
-        <v>3.457787011784612</v>
+        <v>3.459452532593237</v>
       </c>
       <c r="N17" t="n">
-        <v>20.12169530271354</v>
+        <v>20.03226408947595</v>
       </c>
       <c r="O17" t="n">
-        <v>4.48572126895035</v>
+        <v>4.475741736235006</v>
       </c>
       <c r="P17" t="n">
-        <v>361.9824982332254</v>
+        <v>362.0663997538296</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30111,28 +30427,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3090794579848619</v>
+        <v>0.3191248106987182</v>
       </c>
       <c r="J18" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K18" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1319236892837969</v>
+        <v>0.1415692780447216</v>
       </c>
       <c r="M18" t="n">
-        <v>4.327190576915353</v>
+        <v>4.322862222603192</v>
       </c>
       <c r="N18" t="n">
-        <v>34.06535402906487</v>
+        <v>33.92557425955418</v>
       </c>
       <c r="O18" t="n">
-        <v>5.83655326618929</v>
+        <v>5.82456644391273</v>
       </c>
       <c r="P18" t="n">
-        <v>365.9666457566711</v>
+        <v>365.8557446678944</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30189,28 +30505,28 @@
         <v>0.1952</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3769227817199275</v>
+        <v>0.3759560619618743</v>
       </c>
       <c r="J19" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K19" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1866970327921845</v>
+        <v>0.1897020605415825</v>
       </c>
       <c r="M19" t="n">
-        <v>4.447819131726618</v>
+        <v>4.404230932769853</v>
       </c>
       <c r="N19" t="n">
-        <v>33.53954929754952</v>
+        <v>33.16780279861901</v>
       </c>
       <c r="O19" t="n">
-        <v>5.79133398255959</v>
+        <v>5.759149485698302</v>
       </c>
       <c r="P19" t="n">
-        <v>363.1887239588044</v>
+        <v>363.1993910591499</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30267,28 +30583,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3464748323205785</v>
+        <v>0.3573027441168377</v>
       </c>
       <c r="J20" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K20" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L20" t="n">
-        <v>0.16307866065399</v>
+        <v>0.1740879212249385</v>
       </c>
       <c r="M20" t="n">
-        <v>4.52800196248611</v>
+        <v>4.529045157244567</v>
       </c>
       <c r="N20" t="n">
-        <v>33.38630818400213</v>
+        <v>33.27420700524073</v>
       </c>
       <c r="O20" t="n">
-        <v>5.778088627219396</v>
+        <v>5.768379928995725</v>
       </c>
       <c r="P20" t="n">
-        <v>352.4364458783259</v>
+        <v>352.3169281682426</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30326,7 +30642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U356"/>
+  <dimension ref="A1:U360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68397,6 +68713,434 @@
         </is>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-36.79216196266979,175.72829524350462</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-36.79249785700508,175.72748283618466</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-36.79293409638794,175.72674496662682</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-36.79358288149811,175.72608754472913</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-36.794286912818066,175.7255382179339</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-36.79492622503313,175.72511363957724</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-36.79561761937666,175.7248387309492</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-36.79632209629377,175.72461041041356</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-36.79702243805068,175.7243736816132</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-36.797720661384794,175.72409338844332</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-36.79844070467703,175.72392215912762</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-36.79916138481944,175.72379747868587</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-36.79988864752376,175.72370307028922</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-36.800610693271665,175.72366249647794</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>-36.80132669559849,175.72367944526658</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>-36.802039307470885,175.72367762964032</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>-36.80274403787823,175.72381797534263</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>-36.80344294709557,175.72390910212434</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>-36.80415108144122,175.72405641779164</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-36.79215764442475,175.7282910183641</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-36.79249176895756,175.7274768794442</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-36.79293465056642,175.7267455394249</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-36.79359097316109,175.72610196711915</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-36.794291719884725,175.72555355975115</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-36.794929593275484,175.7251243893656</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-36.79561870611651,175.72484229146042</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-36.79632690427305,175.7246265908152</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-36.79702749967747,175.7243911778422</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-36.79772605218639,175.72411464705743</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-36.798445388041856,175.72394286216482</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-36.79916407524433,175.72380980227078</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>-36.79988893873824,175.72370516754447</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-36.800610631260085,175.72366160367196</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>-36.80132672478858,175.72368190937917</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>-36.80203923624726,175.7236790831825</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>-36.802742085744676,175.72383810499448</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>-36.803443088586,175.72390833797698</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>-36.80414657372891,175.72407613640632</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-36.79215360934315,175.72828707028242</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-36.79249325557384,175.727478333997</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-36.79293804490959,175.72674904781337</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-36.79359097316109,175.72610196711915</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-36.79429116396556,175.7255517855273</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-36.794930672420875,175.7251278334727</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-36.795620911558785,175.72484951720418</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-36.79632974535062,175.72463615196253</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-36.79703060983235,175.72440192853819</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-36.797728138073396,175.72412287275307</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-36.798448534675515,175.7239567720192</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-36.79917016409577,175.72383769249225</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-36.79989096191149,175.72371973794992</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-36.80061077078614,175.7236636124854</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>-36.801326722134945,175.72368168536894</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>-36.80203905544873,175.72368277294336</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>-36.80274226909438,175.72383621436427</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>-36.803443755612236,175.723904735568</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>-36.804147977770796,175.72406999454302</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-36.79214702578865,175.72828062867634</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-36.79248709673482,175.72747230799285</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-36.792939083994206,175.7267501218099</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-36.79359427167284,175.72610784631087</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-36.79429302792972,175.7255577343956</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-36.794934563883714,175.72514025313248</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-36.795624779072426,175.72486218843684</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-36.79632743502386,175.72462837696355</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-36.797024541980214,175.72438095414185</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-36.797730115602086,175.72413067114024</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-36.798448705423034,175.72395752681754</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-36.79917068329985,175.72384007072836</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-36.79989375143525,175.7237398274494</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-36.80061123587278,175.72367030853025</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>-36.80132674469091,175.72368358945593</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>-36.802038370604805,175.72369674931016</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>-36.80273983161943,175.72386134862407</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>-36.80344207793999,175.72391379617227</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>-36.804147115639836,175.7240737658626</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0175/nzd0175.xlsx
+++ b/data/nzd0175/nzd0175.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U360"/>
+  <dimension ref="A1:U361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25294,6 +25294,75 @@
       <c r="U360" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>311.98</v>
+      </c>
+      <c r="C361" t="n">
+        <v>297.8</v>
+      </c>
+      <c r="D361" t="n">
+        <v>300.64</v>
+      </c>
+      <c r="E361" t="n">
+        <v>317.71</v>
+      </c>
+      <c r="F361" t="n">
+        <v>303.45</v>
+      </c>
+      <c r="G361" t="n">
+        <v>297.76</v>
+      </c>
+      <c r="H361" t="n">
+        <v>303.82</v>
+      </c>
+      <c r="I361" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="J361" t="n">
+        <v>319.48</v>
+      </c>
+      <c r="K361" t="n">
+        <v>325.47</v>
+      </c>
+      <c r="L361" t="n">
+        <v>334.4</v>
+      </c>
+      <c r="M361" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="N361" t="n">
+        <v>360.96</v>
+      </c>
+      <c r="O361" t="n">
+        <v>362.74</v>
+      </c>
+      <c r="P361" t="n">
+        <v>372.71</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>372.22</v>
+      </c>
+      <c r="R361" t="n">
+        <v>382</v>
+      </c>
+      <c r="S361" t="n">
+        <v>374.53</v>
+      </c>
+      <c r="T361" t="n">
+        <v>367.42</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25308,7 +25377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B370"/>
+  <dimension ref="A1:B371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29011,6 +29080,16 @@
       </c>
       <c r="B370" t="n">
         <v>-0.32</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -29179,28 +29258,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3449456417005079</v>
+        <v>0.3440737421171772</v>
       </c>
       <c r="J2" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K2" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1733708416403398</v>
+        <v>0.1734842626744788</v>
       </c>
       <c r="M2" t="n">
-        <v>4.279963070032792</v>
+        <v>4.272695121125609</v>
       </c>
       <c r="N2" t="n">
-        <v>31.48749305439564</v>
+        <v>31.40697579452783</v>
       </c>
       <c r="O2" t="n">
-        <v>5.611371762269511</v>
+        <v>5.604192697840415</v>
       </c>
       <c r="P2" t="n">
-        <v>304.2387940276628</v>
+        <v>304.2483730134557</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29257,28 +29336,28 @@
         <v>0.1504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06750497853618832</v>
+        <v>-0.06814679606507358</v>
       </c>
       <c r="J3" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K3" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007763568371725982</v>
+        <v>0.007957615797511086</v>
       </c>
       <c r="M3" t="n">
-        <v>4.151055420532471</v>
+        <v>4.143013081238425</v>
       </c>
       <c r="N3" t="n">
-        <v>32.32417812636177</v>
+        <v>32.2381536122137</v>
       </c>
       <c r="O3" t="n">
-        <v>5.685435614476852</v>
+        <v>5.677865233713609</v>
       </c>
       <c r="P3" t="n">
-        <v>300.7953700335567</v>
+        <v>300.8024212595332</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29335,28 +29414,28 @@
         <v>0.1503</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0728006612080358</v>
+        <v>-0.07318065755365563</v>
       </c>
       <c r="J4" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K4" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01042219445938619</v>
+        <v>0.01059311081084358</v>
       </c>
       <c r="M4" t="n">
-        <v>3.930805757548623</v>
+        <v>3.921790126482319</v>
       </c>
       <c r="N4" t="n">
-        <v>27.92952304861855</v>
+        <v>27.85326077177309</v>
       </c>
       <c r="O4" t="n">
-        <v>5.284838980387061</v>
+        <v>5.27761885434834</v>
       </c>
       <c r="P4" t="n">
-        <v>303.2975916470742</v>
+        <v>303.3017664163546</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29413,28 +29492,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04995185710282357</v>
+        <v>-0.04925476671549939</v>
       </c>
       <c r="J5" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K5" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01101131205435291</v>
+        <v>0.01077012440755587</v>
       </c>
       <c r="M5" t="n">
-        <v>2.641716041413675</v>
+        <v>2.63833067372259</v>
       </c>
       <c r="N5" t="n">
-        <v>12.43820267662625</v>
+        <v>12.40809336108446</v>
       </c>
       <c r="O5" t="n">
-        <v>3.526783616360131</v>
+        <v>3.52251236492996</v>
       </c>
       <c r="P5" t="n">
-        <v>317.7871286883428</v>
+        <v>317.7794702159177</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29491,28 +29570,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04748523867438404</v>
+        <v>0.04850437760286722</v>
       </c>
       <c r="J6" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K6" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007501294039281459</v>
+        <v>0.007866999560082411</v>
       </c>
       <c r="M6" t="n">
-        <v>3.136686240966863</v>
+        <v>3.134819540429939</v>
       </c>
       <c r="N6" t="n">
-        <v>16.55819938083391</v>
+        <v>16.52169716580507</v>
       </c>
       <c r="O6" t="n">
-        <v>4.069176744850721</v>
+        <v>4.064689061392651</v>
       </c>
       <c r="P6" t="n">
-        <v>300.3123369866958</v>
+        <v>300.3011403793072</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29569,28 +29648,28 @@
         <v>0.0881</v>
       </c>
       <c r="I7" t="n">
-        <v>0.111105376607242</v>
+        <v>0.1128573452744151</v>
       </c>
       <c r="J7" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K7" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0301195317470464</v>
+        <v>0.03119189967410452</v>
       </c>
       <c r="M7" t="n">
-        <v>3.772982990727903</v>
+        <v>3.771653349657467</v>
       </c>
       <c r="N7" t="n">
-        <v>22.0618662219705</v>
+        <v>22.02863626935066</v>
       </c>
       <c r="O7" t="n">
-        <v>4.697006091327805</v>
+        <v>4.693467403674032</v>
       </c>
       <c r="P7" t="n">
-        <v>291.5598679687994</v>
+        <v>291.5406202442986</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29647,28 +29726,28 @@
         <v>0.1029</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3445229923471364</v>
+        <v>0.3462167008955557</v>
       </c>
       <c r="J8" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K8" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1713135929927209</v>
+        <v>0.1734618341553563</v>
       </c>
       <c r="M8" t="n">
-        <v>4.545094734636794</v>
+        <v>4.54202451567406</v>
       </c>
       <c r="N8" t="n">
-        <v>31.86668667150159</v>
+        <v>31.80438637408223</v>
       </c>
       <c r="O8" t="n">
-        <v>5.645058606560394</v>
+        <v>5.639537780180414</v>
       </c>
       <c r="P8" t="n">
-        <v>291.4111676767557</v>
+        <v>291.3925600177631</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29725,28 +29804,28 @@
         <v>0.1076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2956614247318045</v>
+        <v>0.2980649446973561</v>
       </c>
       <c r="J9" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K9" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1257592208281197</v>
+        <v>0.1280525693363535</v>
       </c>
       <c r="M9" t="n">
-        <v>4.738527136325964</v>
+        <v>4.737004802667474</v>
       </c>
       <c r="N9" t="n">
-        <v>33.72738348971888</v>
+        <v>33.68649489441984</v>
       </c>
       <c r="O9" t="n">
-        <v>5.807528173820501</v>
+        <v>5.80400679655183</v>
       </c>
       <c r="P9" t="n">
-        <v>299.9705360184526</v>
+        <v>299.9441301294685</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29803,28 +29882,28 @@
         <v>0.1135</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1669663216002085</v>
+        <v>0.1696016977479932</v>
       </c>
       <c r="J10" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K10" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05007744887664189</v>
+        <v>0.05178009033909137</v>
       </c>
       <c r="M10" t="n">
-        <v>4.351919248611699</v>
+        <v>4.354400678496446</v>
       </c>
       <c r="N10" t="n">
-        <v>29.34984811017902</v>
+        <v>29.33179711290839</v>
       </c>
       <c r="O10" t="n">
-        <v>5.417550009937981</v>
+        <v>5.415883779486815</v>
       </c>
       <c r="P10" t="n">
-        <v>310.1593026166126</v>
+        <v>310.1303494766399</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29881,28 +29960,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2600726040973741</v>
+        <v>0.261442936187151</v>
       </c>
       <c r="J11" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K11" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1246569889382021</v>
+        <v>0.1264040522434595</v>
       </c>
       <c r="M11" t="n">
-        <v>3.816856357939955</v>
+        <v>3.812696886334739</v>
       </c>
       <c r="N11" t="n">
-        <v>26.46734405512959</v>
+        <v>26.41068658418338</v>
       </c>
       <c r="O11" t="n">
-        <v>5.144642266973437</v>
+        <v>5.13913286306001</v>
       </c>
       <c r="P11" t="n">
-        <v>315.9381587295577</v>
+        <v>315.9231155196875</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29959,28 +30038,28 @@
         <v>0.1208</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2041948657062745</v>
+        <v>0.2069157289745398</v>
       </c>
       <c r="J12" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K12" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0641867081937747</v>
+        <v>0.06604567554009555</v>
       </c>
       <c r="M12" t="n">
-        <v>4.530808331272719</v>
+        <v>4.530424512433504</v>
       </c>
       <c r="N12" t="n">
-        <v>33.73928224099156</v>
+        <v>33.71322329395427</v>
       </c>
       <c r="O12" t="n">
-        <v>5.808552508240892</v>
+        <v>5.806308921677719</v>
       </c>
       <c r="P12" t="n">
-        <v>323.9156089926469</v>
+        <v>323.8857166620514</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30037,28 +30116,28 @@
         <v>0.1693</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2176253176905744</v>
+        <v>0.2219796102646429</v>
       </c>
       <c r="J13" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K13" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08198180884673645</v>
+        <v>0.08502817903414495</v>
       </c>
       <c r="M13" t="n">
-        <v>4.153527019315558</v>
+        <v>4.15944118430138</v>
       </c>
       <c r="N13" t="n">
-        <v>29.43436862566851</v>
+        <v>29.52589190000427</v>
       </c>
       <c r="O13" t="n">
-        <v>5.425345023652276</v>
+        <v>5.433773265421025</v>
       </c>
       <c r="P13" t="n">
-        <v>333.6762809880516</v>
+        <v>333.628443246754</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30115,28 +30194,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1587333918144416</v>
+        <v>0.1624298388383092</v>
       </c>
       <c r="J14" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K14" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05139256402653847</v>
+        <v>0.05374675496551118</v>
       </c>
       <c r="M14" t="n">
-        <v>3.819354929820201</v>
+        <v>3.821107493644489</v>
       </c>
       <c r="N14" t="n">
-        <v>25.81219452258496</v>
+        <v>25.86537480631811</v>
       </c>
       <c r="O14" t="n">
-        <v>5.080570295014621</v>
+        <v>5.085801294419406</v>
       </c>
       <c r="P14" t="n">
-        <v>349.9324160305046</v>
+        <v>349.8918056044849</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30193,28 +30272,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2371714799790894</v>
+        <v>0.2387927195613729</v>
       </c>
       <c r="J15" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K15" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1004092991853535</v>
+        <v>0.1021237580602943</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95562859844839</v>
+        <v>3.950925451339232</v>
       </c>
       <c r="N15" t="n">
-        <v>27.97035937208535</v>
+        <v>27.91668659410245</v>
       </c>
       <c r="O15" t="n">
-        <v>5.288701104438154</v>
+        <v>5.283624380489443</v>
       </c>
       <c r="P15" t="n">
-        <v>353.3670576096966</v>
+        <v>353.3492461194489</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30271,28 +30350,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3281380989658074</v>
+        <v>0.3297267759794981</v>
       </c>
       <c r="J16" t="n">
+        <v>360</v>
+      </c>
+      <c r="K16" t="n">
         <v>359</v>
       </c>
-      <c r="K16" t="n">
-        <v>358</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1936364276109075</v>
+        <v>0.1959577643490957</v>
       </c>
       <c r="M16" t="n">
-        <v>3.853541005465373</v>
+        <v>3.847385194504647</v>
       </c>
       <c r="N16" t="n">
-        <v>24.86718840517504</v>
+        <v>24.8209862490753</v>
       </c>
       <c r="O16" t="n">
-        <v>4.986701154588576</v>
+        <v>4.982066463735234</v>
       </c>
       <c r="P16" t="n">
-        <v>360.9398586204454</v>
+        <v>360.9223785050735</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30349,28 +30428,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3663240032958309</v>
+        <v>0.3664597233122855</v>
       </c>
       <c r="J17" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K17" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2710277729132992</v>
+        <v>0.2723746525512929</v>
       </c>
       <c r="M17" t="n">
-        <v>3.459452532593237</v>
+        <v>3.450486421144854</v>
       </c>
       <c r="N17" t="n">
-        <v>20.03226408947595</v>
+        <v>19.97678726201931</v>
       </c>
       <c r="O17" t="n">
-        <v>4.475741736235006</v>
+        <v>4.469539938519323</v>
       </c>
       <c r="P17" t="n">
-        <v>362.0663997538296</v>
+        <v>362.0649086875024</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30427,28 +30506,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3191248106987182</v>
+        <v>0.3232857651362904</v>
       </c>
       <c r="J18" t="n">
+        <v>360</v>
+      </c>
+      <c r="K18" t="n">
         <v>359</v>
       </c>
-      <c r="K18" t="n">
-        <v>358</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1415692780447216</v>
+        <v>0.1449338655633245</v>
       </c>
       <c r="M18" t="n">
-        <v>4.322862222603192</v>
+        <v>4.329186376809538</v>
       </c>
       <c r="N18" t="n">
-        <v>33.92557425955418</v>
+        <v>33.98694989173985</v>
       </c>
       <c r="O18" t="n">
-        <v>5.82456644391273</v>
+        <v>5.829832749894275</v>
       </c>
       <c r="P18" t="n">
-        <v>365.8557446678944</v>
+        <v>365.8097166726223</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30505,28 +30584,28 @@
         <v>0.1952</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3759560619618743</v>
+        <v>0.3766004987110529</v>
       </c>
       <c r="J19" t="n">
+        <v>360</v>
+      </c>
+      <c r="K19" t="n">
         <v>359</v>
       </c>
-      <c r="K19" t="n">
-        <v>358</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.1897020605415825</v>
+        <v>0.1911536643007663</v>
       </c>
       <c r="M19" t="n">
-        <v>4.404230932769853</v>
+        <v>4.394332520106613</v>
       </c>
       <c r="N19" t="n">
-        <v>33.16780279861901</v>
+        <v>33.07915235869087</v>
       </c>
       <c r="O19" t="n">
-        <v>5.759149485698302</v>
+        <v>5.751447848906471</v>
       </c>
       <c r="P19" t="n">
-        <v>363.1993910591499</v>
+        <v>363.1922623745922</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30583,28 +30662,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3573027441168377</v>
+        <v>0.3603121274305129</v>
       </c>
       <c r="J20" t="n">
+        <v>360</v>
+      </c>
+      <c r="K20" t="n">
         <v>359</v>
       </c>
-      <c r="K20" t="n">
-        <v>358</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.1740879212249385</v>
+        <v>0.1770440670264062</v>
       </c>
       <c r="M20" t="n">
-        <v>4.529045157244567</v>
+        <v>4.531012385389982</v>
       </c>
       <c r="N20" t="n">
-        <v>33.27420700524073</v>
+        <v>33.26305691000922</v>
       </c>
       <c r="O20" t="n">
-        <v>5.768379928995725</v>
+        <v>5.767413363892796</v>
       </c>
       <c r="P20" t="n">
-        <v>352.3169281682426</v>
+        <v>352.2836387191482</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30642,7 +30721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U360"/>
+  <dimension ref="A1:U361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69141,6 +69220,113 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-36.792155308324894,175.72828873263256</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-36.79248879572492,175.72747397033874</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-36.79295148373645,175.72676293817074</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-36.793600301763824,175.72611859420945</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-36.794297246373795,175.7255711976249</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-36.794943818365525,175.72516978896684</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-36.79563292961307,175.72488889227827</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-36.796333585487176,175.7246490752726</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-36.797028658362734,175.72439518300334</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-36.79773249947159,175.72414007193623</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-36.798452169157265,175.72397283844148</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-36.79917372772275,175.72385401584077</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-36.799895851239306,175.72375494976578</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-36.800611894744854,175.72367979459383</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>-36.801326899928135,175.7236966940546</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>-36.80203701186961,175.7237244784208</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>-36.8027386344506,175.7238736933262</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>-36.803439733240296,175.7239264591847</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>-36.804146302773425,175.72407732167815</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0175/nzd0175.xlsx
+++ b/data/nzd0175/nzd0175.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U361"/>
+  <dimension ref="A1:U362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25363,6 +25363,75 @@
       <c r="U361" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>310.96</v>
+      </c>
+      <c r="C362" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="D362" t="n">
+        <v>300.64</v>
+      </c>
+      <c r="E362" t="n">
+        <v>317.24</v>
+      </c>
+      <c r="F362" t="n">
+        <v>303.11</v>
+      </c>
+      <c r="G362" t="n">
+        <v>298.94</v>
+      </c>
+      <c r="H362" t="n">
+        <v>305.07</v>
+      </c>
+      <c r="I362" t="n">
+        <v>312.7</v>
+      </c>
+      <c r="J362" t="n">
+        <v>320.4</v>
+      </c>
+      <c r="K362" t="n">
+        <v>325.63</v>
+      </c>
+      <c r="L362" t="n">
+        <v>336.96</v>
+      </c>
+      <c r="M362" t="n">
+        <v>347.45</v>
+      </c>
+      <c r="N362" t="n">
+        <v>362.22</v>
+      </c>
+      <c r="O362" t="n">
+        <v>363.78</v>
+      </c>
+      <c r="P362" t="n">
+        <v>373.58</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>374.61</v>
+      </c>
+      <c r="R362" t="n">
+        <v>382.65</v>
+      </c>
+      <c r="S362" t="n">
+        <v>373.91</v>
+      </c>
+      <c r="T362" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25377,7 +25446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B371"/>
+  <dimension ref="A1:B372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29090,6 +29159,16 @@
       </c>
       <c r="B371" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -29258,28 +29337,28 @@
         <v>0.1008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3440737421171772</v>
+        <v>0.3426263954378972</v>
       </c>
       <c r="J2" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K2" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1734842626744788</v>
+        <v>0.1730666814875274</v>
       </c>
       <c r="M2" t="n">
-        <v>4.272695121125609</v>
+        <v>4.268490572302604</v>
       </c>
       <c r="N2" t="n">
-        <v>31.40697579452783</v>
+        <v>31.33902936365578</v>
       </c>
       <c r="O2" t="n">
-        <v>5.604192697840415</v>
+        <v>5.598127308632395</v>
       </c>
       <c r="P2" t="n">
-        <v>304.2483730134557</v>
+        <v>304.264346247414</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29336,28 +29415,28 @@
         <v>0.1504</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06814679606507358</v>
+        <v>-0.06979468944832726</v>
       </c>
       <c r="J3" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K3" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007957615797511086</v>
+        <v>0.008388306428349646</v>
       </c>
       <c r="M3" t="n">
-        <v>4.143013081238425</v>
+        <v>4.140374056620693</v>
       </c>
       <c r="N3" t="n">
-        <v>32.2381536122137</v>
+        <v>32.17355073237605</v>
       </c>
       <c r="O3" t="n">
-        <v>5.677865233713609</v>
+        <v>5.672173369386381</v>
       </c>
       <c r="P3" t="n">
-        <v>300.8024212595332</v>
+        <v>300.8206077707027</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29414,28 +29493,28 @@
         <v>0.1503</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07318065755365563</v>
+        <v>-0.07355352385345795</v>
       </c>
       <c r="J4" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K4" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01059311081084358</v>
+        <v>0.0107647100312287</v>
       </c>
       <c r="M4" t="n">
-        <v>3.921790126482319</v>
+        <v>3.912768326571898</v>
       </c>
       <c r="N4" t="n">
-        <v>27.85326077177309</v>
+        <v>27.77736947456653</v>
       </c>
       <c r="O4" t="n">
-        <v>5.27761885434834</v>
+        <v>5.270424031761253</v>
       </c>
       <c r="P4" t="n">
-        <v>303.3017664163546</v>
+        <v>303.3058814502487</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29492,28 +29571,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04925476671549939</v>
+        <v>-0.04881435842170947</v>
       </c>
       <c r="J5" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K5" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01077012440755587</v>
+        <v>0.01064321230000531</v>
       </c>
       <c r="M5" t="n">
-        <v>2.63833067372259</v>
+        <v>2.633498136496681</v>
       </c>
       <c r="N5" t="n">
-        <v>12.40809336108446</v>
+        <v>12.37548608222074</v>
       </c>
       <c r="O5" t="n">
-        <v>3.52251236492996</v>
+        <v>3.517880907907592</v>
       </c>
       <c r="P5" t="n">
-        <v>317.7794702159177</v>
+        <v>317.774609773831</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29570,28 +29649,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04850437760286722</v>
+        <v>0.04932547954268857</v>
       </c>
       <c r="J6" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K6" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007866999560082411</v>
+        <v>0.008179953346734492</v>
       </c>
       <c r="M6" t="n">
-        <v>3.134819540429939</v>
+        <v>3.131595039363072</v>
       </c>
       <c r="N6" t="n">
-        <v>16.52169716580507</v>
+        <v>16.48206299783079</v>
       </c>
       <c r="O6" t="n">
-        <v>4.064689061392651</v>
+        <v>4.059810709605904</v>
       </c>
       <c r="P6" t="n">
-        <v>300.3011403793072</v>
+        <v>300.2920785190245</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29648,28 +29727,28 @@
         <v>0.0881</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1128573452744151</v>
+        <v>0.1152386319330325</v>
       </c>
       <c r="J7" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K7" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03119189967410452</v>
+        <v>0.03259783458005927</v>
       </c>
       <c r="M7" t="n">
-        <v>3.771653349657467</v>
+        <v>3.77351355247966</v>
       </c>
       <c r="N7" t="n">
-        <v>22.02863626935066</v>
+        <v>22.01919175445786</v>
       </c>
       <c r="O7" t="n">
-        <v>4.693467403674032</v>
+        <v>4.692461161742083</v>
       </c>
       <c r="P7" t="n">
-        <v>291.5406202442986</v>
+        <v>291.514339844817</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29726,28 +29805,28 @@
         <v>0.1029</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3462167008955557</v>
+        <v>0.3485667487300877</v>
       </c>
       <c r="J8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1734618341553563</v>
+        <v>0.1760680403630182</v>
       </c>
       <c r="M8" t="n">
-        <v>4.54202451567406</v>
+        <v>4.542555334279775</v>
       </c>
       <c r="N8" t="n">
-        <v>31.80438637408223</v>
+        <v>31.7665178824686</v>
       </c>
       <c r="O8" t="n">
-        <v>5.639537780180414</v>
+        <v>5.636179369259694</v>
       </c>
       <c r="P8" t="n">
-        <v>291.3925600177631</v>
+        <v>291.3666243767647</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29804,28 +29883,28 @@
         <v>0.1076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2980649446973561</v>
+        <v>0.3006233337720038</v>
       </c>
       <c r="J9" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K9" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1280525693363535</v>
+        <v>0.1304663602057846</v>
       </c>
       <c r="M9" t="n">
-        <v>4.737004802667474</v>
+        <v>4.736117965577846</v>
       </c>
       <c r="N9" t="n">
-        <v>33.68649489441984</v>
+        <v>33.6527142017347</v>
       </c>
       <c r="O9" t="n">
-        <v>5.80400679655183</v>
+        <v>5.801095948330341</v>
       </c>
       <c r="P9" t="n">
-        <v>299.9441301294685</v>
+        <v>299.915895189056</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29882,28 +29961,28 @@
         <v>0.1135</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1696016977479932</v>
+        <v>0.1727126736520416</v>
       </c>
       <c r="J10" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K10" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05178009033909137</v>
+        <v>0.05375277784165944</v>
       </c>
       <c r="M10" t="n">
-        <v>4.354400678496446</v>
+        <v>4.359379115344247</v>
       </c>
       <c r="N10" t="n">
-        <v>29.33179711290839</v>
+        <v>29.33857402978946</v>
       </c>
       <c r="O10" t="n">
-        <v>5.415883779486815</v>
+        <v>5.416509395338428</v>
       </c>
       <c r="P10" t="n">
-        <v>310.1303494766399</v>
+        <v>310.0960160673293</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29960,28 +30039,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.261442936187151</v>
+        <v>0.2628764211902494</v>
       </c>
       <c r="J11" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K11" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1264040522434595</v>
+        <v>0.1282184667798878</v>
       </c>
       <c r="M11" t="n">
-        <v>3.812696886334739</v>
+        <v>3.808835780058236</v>
       </c>
       <c r="N11" t="n">
-        <v>26.41068658418338</v>
+        <v>26.35592963840894</v>
       </c>
       <c r="O11" t="n">
-        <v>5.13913286306001</v>
+        <v>5.133802648954179</v>
       </c>
       <c r="P11" t="n">
-        <v>315.9231155196875</v>
+        <v>315.907306957745</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30038,28 +30117,28 @@
         <v>0.1208</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2069157289745398</v>
+        <v>0.2110108162927144</v>
       </c>
       <c r="J12" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K12" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06604567554009555</v>
+        <v>0.06860690904080768</v>
       </c>
       <c r="M12" t="n">
-        <v>4.530424512433504</v>
+        <v>4.536019872703658</v>
       </c>
       <c r="N12" t="n">
-        <v>33.71322329395427</v>
+        <v>33.77236512239212</v>
       </c>
       <c r="O12" t="n">
-        <v>5.806308921677719</v>
+        <v>5.811399583782904</v>
       </c>
       <c r="P12" t="n">
-        <v>323.8857166620514</v>
+        <v>323.8405223843091</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30116,28 +30195,28 @@
         <v>0.1693</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2219796102646429</v>
+        <v>0.2262626773874403</v>
       </c>
       <c r="J13" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K13" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08502817903414495</v>
+        <v>0.08808734366765436</v>
       </c>
       <c r="M13" t="n">
-        <v>4.15944118430138</v>
+        <v>4.164876216804887</v>
       </c>
       <c r="N13" t="n">
-        <v>29.52589190000427</v>
+        <v>29.61095780621983</v>
       </c>
       <c r="O13" t="n">
-        <v>5.433773265421025</v>
+        <v>5.441595152730478</v>
       </c>
       <c r="P13" t="n">
-        <v>333.628443246754</v>
+        <v>333.5811743828454</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30194,28 +30273,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1624298388383092</v>
+        <v>0.1667771755195299</v>
       </c>
       <c r="J14" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K14" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05374675496551118</v>
+        <v>0.05646990729022372</v>
       </c>
       <c r="M14" t="n">
-        <v>3.821107493644489</v>
+        <v>3.825112185507923</v>
       </c>
       <c r="N14" t="n">
-        <v>25.86537480631811</v>
+        <v>25.96562570641183</v>
       </c>
       <c r="O14" t="n">
-        <v>5.085801294419406</v>
+        <v>5.09564772196939</v>
       </c>
       <c r="P14" t="n">
-        <v>349.8918056044849</v>
+        <v>349.8438274476972</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30272,28 +30351,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2387927195613729</v>
+        <v>0.2409614023038281</v>
       </c>
       <c r="J15" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K15" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1021237580602943</v>
+        <v>0.1042213202864228</v>
       </c>
       <c r="M15" t="n">
-        <v>3.950925451339232</v>
+        <v>3.948280738448444</v>
       </c>
       <c r="N15" t="n">
-        <v>27.91668659410245</v>
+        <v>27.88213317487493</v>
       </c>
       <c r="O15" t="n">
-        <v>5.283624380489443</v>
+        <v>5.280353508513889</v>
       </c>
       <c r="P15" t="n">
-        <v>353.3492461194489</v>
+        <v>353.3253120632048</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30350,28 +30429,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3297267759794981</v>
+        <v>0.3317660667260486</v>
       </c>
       <c r="J16" t="n">
+        <v>361</v>
+      </c>
+      <c r="K16" t="n">
         <v>360</v>
       </c>
-      <c r="K16" t="n">
-        <v>359</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1959577643490957</v>
+        <v>0.1986380686841464</v>
       </c>
       <c r="M16" t="n">
-        <v>3.847385194504647</v>
+        <v>3.842495250609786</v>
       </c>
       <c r="N16" t="n">
-        <v>24.8209862490753</v>
+        <v>24.789860628733</v>
       </c>
       <c r="O16" t="n">
-        <v>4.982066463735234</v>
+        <v>4.978941717748159</v>
       </c>
       <c r="P16" t="n">
-        <v>360.9223785050735</v>
+        <v>360.8998382454698</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30428,28 +30507,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3664597233122855</v>
+        <v>0.3678822847782877</v>
       </c>
       <c r="J17" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K17" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2723746525512929</v>
+        <v>0.2749485487026193</v>
       </c>
       <c r="M17" t="n">
-        <v>3.450486421144854</v>
+        <v>3.447678835052498</v>
       </c>
       <c r="N17" t="n">
-        <v>19.97678726201931</v>
+        <v>19.93985642404122</v>
       </c>
       <c r="O17" t="n">
-        <v>4.469539938519323</v>
+        <v>4.465406635911361</v>
       </c>
       <c r="P17" t="n">
-        <v>362.0649086875024</v>
+        <v>362.0492089885693</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30506,28 +30585,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3232857651362904</v>
+        <v>0.3277542352519532</v>
       </c>
       <c r="J18" t="n">
+        <v>361</v>
+      </c>
+      <c r="K18" t="n">
         <v>360</v>
       </c>
-      <c r="K18" t="n">
-        <v>359</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1449338655633245</v>
+        <v>0.1484819642851198</v>
       </c>
       <c r="M18" t="n">
-        <v>4.329186376809538</v>
+        <v>4.336870389478435</v>
       </c>
       <c r="N18" t="n">
-        <v>33.98694989173985</v>
+        <v>34.07144063870204</v>
       </c>
       <c r="O18" t="n">
-        <v>5.829832749894275</v>
+        <v>5.83707466447895</v>
       </c>
       <c r="P18" t="n">
-        <v>365.8097166726223</v>
+        <v>365.7600645610343</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30584,28 +30663,28 @@
         <v>0.1952</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3766004987110529</v>
+        <v>0.3768712658484226</v>
       </c>
       <c r="J19" t="n">
+        <v>361</v>
+      </c>
+      <c r="K19" t="n">
         <v>360</v>
       </c>
-      <c r="K19" t="n">
-        <v>359</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.1911536643007663</v>
+        <v>0.1923270421417215</v>
       </c>
       <c r="M19" t="n">
-        <v>4.394332520106613</v>
+        <v>4.383126170994744</v>
       </c>
       <c r="N19" t="n">
-        <v>33.07915235869087</v>
+        <v>32.98792269819355</v>
       </c>
       <c r="O19" t="n">
-        <v>5.751447848906471</v>
+        <v>5.743511356147348</v>
       </c>
       <c r="P19" t="n">
-        <v>363.1922623745922</v>
+        <v>363.1892537027713</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30662,28 +30741,28 @@
         <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3603121274305129</v>
+        <v>0.3635496387973416</v>
       </c>
       <c r="J20" t="n">
+        <v>361</v>
+      </c>
+      <c r="K20" t="n">
         <v>360</v>
       </c>
-      <c r="K20" t="n">
-        <v>359</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.1770440670264062</v>
+        <v>0.1801565926509127</v>
       </c>
       <c r="M20" t="n">
-        <v>4.531012385389982</v>
+        <v>4.533935112260776</v>
       </c>
       <c r="N20" t="n">
-        <v>33.26305691000922</v>
+        <v>33.26456970650867</v>
       </c>
       <c r="O20" t="n">
-        <v>5.767413363892796</v>
+        <v>5.767544512746189</v>
       </c>
       <c r="P20" t="n">
-        <v>352.2836387191482</v>
+        <v>352.2476646001562</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30721,7 +30800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U361"/>
+  <dimension ref="A1:U362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69327,6 +69406,113 @@
         </is>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-36.7921480876523,175.728281667645</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-36.792475699342106,175.72746115642448</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-36.79295148373645,175.72676293817074</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-36.7935978794197,175.72611427667732</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-36.79429613453597,175.72556764917675</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-36.79494767712246,175.72518210426372</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-36.79563692497385,175.7249019823986</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-36.796334678208694,175.7246527526375</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-36.797031463600185,175.7244048797098</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-36.79773293290233,175.7241417811719</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-36.798458413630755,175.72400044249912</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-36.79917360972189,175.72385347533253</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-36.79989778244425,175.7237688578822</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-36.80061270089319,175.72369140107182</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-36.80132701536002,175.72370643849973</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>-36.802035702437266,175.72375120123175</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>-36.802737933405204,175.72388092220564</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>-36.803440986442034,175.72391969102296</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>-36.804145095789735,175.7240826015253</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
